--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_25_5.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_25_5.xlsx
@@ -513,1376 +513,1376 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_1</t>
+          <t>model_25_5_24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9992546213943929</v>
+        <v>0.9998713730676326</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7129380810563235</v>
+        <v>0.7058131237596517</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9968375541334413</v>
+        <v>0.9987762514763262</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9961537070017339</v>
+        <v>0.9990160629702706</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9967770365202334</v>
+        <v>0.9995618974649717</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000442488938967542</v>
+        <v>7.635850344745743e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1704123555141846</v>
+        <v>0.1746420379476182</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001247581455261806</v>
+        <v>0.00030359098911015</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001517974409134424</v>
+        <v>0.0001699970258800133</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001382777932198115</v>
+        <v>0.0002367933724068147</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004859005746687402</v>
+        <v>0.003423378206100114</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02103542105515224</v>
+        <v>0.008738335278956596</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000526149603958</v>
+        <v>1.000090795481671</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02193094247879461</v>
+        <v>0.009110344302629496</v>
       </c>
       <c r="P2" t="n">
-        <v>131.4461901810245</v>
+        <v>134.9601423158879</v>
       </c>
       <c r="Q2" t="n">
-        <v>202.1409880233801</v>
+        <v>205.6549401582435</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_4</t>
+          <t>model_25_5_23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9992546077619563</v>
+        <v>0.999872466050916</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7129380802394716</v>
+        <v>0.7057827465313455</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9968375015219991</v>
+        <v>0.9987899619634442</v>
       </c>
       <c r="E3" t="n">
-        <v>0.996153627291839</v>
+        <v>0.9990248471429856</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9967769775718224</v>
+        <v>0.9995664462648608</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004424970317708465</v>
+        <v>7.570966135601579e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1704123559991032</v>
+        <v>0.1746600711825687</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001247602210418551</v>
+        <v>0.0003001896527532099</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001518005867367237</v>
+        <v>0.0001684793644939264</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001382803223381968</v>
+        <v>0.0002343347569457349</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004858986381847877</v>
+        <v>0.003429266971520117</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02103561341560655</v>
+        <v>0.008701129889618691</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000526159226854</v>
+        <v>1.000090023964059</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02193114302843171</v>
+        <v>0.009071555002841706</v>
       </c>
       <c r="P3" t="n">
-        <v>131.4461536028026</v>
+        <v>134.9772095575373</v>
       </c>
       <c r="Q3" t="n">
-        <v>202.1409514451582</v>
+        <v>205.6720073998929</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_5</t>
+          <t>model_25_5_22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9992546077619563</v>
+        <v>0.9998736521006607</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7129380802394716</v>
+        <v>0.7057487130155231</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9968375015219991</v>
+        <v>0.9988051614378139</v>
       </c>
       <c r="E4" t="n">
-        <v>0.996153627291839</v>
+        <v>0.9990346160790283</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9967769775718224</v>
+        <v>0.9995714972177856</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004424970317708465</v>
+        <v>7.500557099286186e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1704123559991032</v>
+        <v>0.1746802749477322</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001247602210418551</v>
+        <v>0.0002964189242345537</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001518005867367237</v>
+        <v>0.0001667915633205579</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001382803223381968</v>
+        <v>0.0002316047289698677</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004858986381847877</v>
+        <v>0.003435764031783745</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02103561341560655</v>
+        <v>0.00866057567329458</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000526159226854</v>
+        <v>1.000089186752475</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02193114302843171</v>
+        <v>0.009029274309569875</v>
       </c>
       <c r="P4" t="n">
-        <v>131.4461536028026</v>
+        <v>134.9958963345635</v>
       </c>
       <c r="Q4" t="n">
-        <v>202.1409514451582</v>
+        <v>205.6906941769191</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_6</t>
+          <t>model_25_5_21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9992546077619563</v>
+        <v>0.9998749195394615</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7129380802394716</v>
+        <v>0.7057103714847079</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9968375015219991</v>
+        <v>0.998821904107002</v>
       </c>
       <c r="E5" t="n">
-        <v>0.996153627291839</v>
+        <v>0.9990453974152691</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9967769775718224</v>
+        <v>0.999577061770508</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004424970317708465</v>
+        <v>7.42531645702082e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1704123559991032</v>
+        <v>0.174703036136692</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001247602210418551</v>
+        <v>0.0002922653555880504</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001518005867367237</v>
+        <v>0.0001649288474753786</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001382803223381968</v>
+        <v>0.0002285971015317145</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004858986381847877</v>
+        <v>0.003443022351156949</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02103561341560655</v>
+        <v>0.008617027594838501</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000526159226854</v>
+        <v>1.000088292089792</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02193114302843171</v>
+        <v>0.00898387229925697</v>
       </c>
       <c r="P5" t="n">
-        <v>131.4461536028026</v>
+        <v>135.016060321431</v>
       </c>
       <c r="Q5" t="n">
-        <v>202.1409514451582</v>
+        <v>205.7108581637866</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_3</t>
+          <t>model_25_5_20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9992546143919125</v>
+        <v>0.9998762750510707</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7129380772889149</v>
+        <v>0.7056673863650651</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9968375294216835</v>
+        <v>0.998840422308513</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9961536644884253</v>
+        <v>0.9990572699522503</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9967770062393644</v>
+        <v>0.9995832091545857</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004424930959423779</v>
+        <v>7.344847432394964e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1704123577506811</v>
+        <v>0.1747285539605725</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001247591204023409</v>
+        <v>0.0002876713078694961</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001517991187397124</v>
+        <v>0.0001628776024104265</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001382790923880397</v>
+        <v>0.0002252744551399613</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004858967825559518</v>
+        <v>0.003451004267355143</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02103551986384881</v>
+        <v>0.008570208534449418</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000526154546885</v>
+        <v>1.000087335258068</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02193104549398196</v>
+        <v>0.00893506005453831</v>
       </c>
       <c r="P6" t="n">
-        <v>131.4461713920562</v>
+        <v>135.0378528543755</v>
       </c>
       <c r="Q6" t="n">
-        <v>202.1409692344119</v>
+        <v>205.7326506967312</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_0</t>
+          <t>model_25_5_19</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9992546228779866</v>
+        <v>0.999877721189161</v>
       </c>
       <c r="C7" t="n">
-        <v>0.712938074712048</v>
+        <v>0.7056187959081305</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9968375725562028</v>
+        <v>0.998860928683909</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9961537011588837</v>
+        <v>0.9990704482060022</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9967770423027175</v>
+        <v>0.9995900212582954</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0004424880582422786</v>
+        <v>7.258998428367122e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1704123592804206</v>
+        <v>0.1747573993548073</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001247574187502457</v>
+        <v>0.000282584028359763</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00151797671506824</v>
+        <v>0.0001606007657060208</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001382775451285348</v>
+        <v>0.000221592529376816</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004859027366080672</v>
+        <v>0.003459703954224797</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02103540012080299</v>
+        <v>0.008519975603466902</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000526148556715</v>
+        <v>1.00008631445471</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02193092065322678</v>
+        <v>0.008882688603687367</v>
       </c>
       <c r="P7" t="n">
-        <v>131.4461941618071</v>
+        <v>135.0613672063515</v>
       </c>
       <c r="Q7" t="n">
-        <v>202.1409920041627</v>
+        <v>205.7561650487071</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_2</t>
+          <t>model_25_5_18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9992546181018439</v>
+        <v>0.9998792412232983</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7129380707608797</v>
+        <v>0.7055641117662705</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9968375615613284</v>
+        <v>0.9988834813224107</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9961536672434929</v>
+        <v>0.9990850216586643</v>
       </c>
       <c r="F8" t="n">
-        <v>0.996777022282596</v>
+        <v>0.9995975245994381</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0004424908935668998</v>
+        <v>7.16876263576529e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1704123616260049</v>
+        <v>0.1747898622236473</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00124757852496843</v>
+        <v>0.0002769891061209891</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00151799010008475</v>
+        <v>0.0001580828773305349</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001382784040703826</v>
+        <v>0.0002175369914343944</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004859018857233381</v>
+        <v>0.003469442224752357</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02103546751481649</v>
+        <v>0.008466854572841848</v>
       </c>
       <c r="N8" t="n">
-        <v>1.00052615192811</v>
+        <v>1.000085241489437</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02193099091634295</v>
+        <v>0.008827306100812908</v>
       </c>
       <c r="P8" t="n">
-        <v>131.4461813464758</v>
+        <v>135.0863848009172</v>
       </c>
       <c r="Q8" t="n">
-        <v>202.1409791888314</v>
+        <v>205.7811826432728</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_10</t>
+          <t>model_25_5_17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9992546060462141</v>
+        <v>0.9998808352157842</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7129380685938354</v>
+        <v>0.7055024156701091</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9968374712704674</v>
+        <v>0.9989084671225473</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9961536441545991</v>
+        <v>0.9991010693070485</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9967769617563873</v>
+        <v>0.9996058240617928</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0004424980503095541</v>
+        <v>7.074136356113552e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1704123629124559</v>
+        <v>0.1748264876914613</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001247614144614882</v>
+        <v>0.000270790558273583</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001517999212326032</v>
+        <v>0.0001553102888261549</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001382810008824885</v>
+        <v>0.0002130511518808932</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004858920338541387</v>
+        <v>0.003480091675163362</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02103563762545728</v>
+        <v>0.008410788521960085</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000526160437966</v>
+        <v>1.00008411631827</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0219311682689459</v>
+        <v>0.008768853202072385</v>
       </c>
       <c r="P9" t="n">
-        <v>131.4461489992122</v>
+        <v>135.1129601973986</v>
       </c>
       <c r="Q9" t="n">
-        <v>202.1409468415678</v>
+        <v>205.8077580397543</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_8</t>
+          <t>model_25_5_16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9992546052461204</v>
+        <v>0.9998824825980552</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7129380640901525</v>
+        <v>0.7054325404763238</v>
       </c>
       <c r="D10" t="n">
-        <v>0.996837449107013</v>
+        <v>0.9989359528738612</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9961536587878077</v>
+        <v>0.9991188167557772</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9967769666930346</v>
+        <v>0.9996149679576446</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0004424985252797051</v>
+        <v>6.976340628187901e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1704123655860366</v>
+        <v>0.1748679686249435</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001247622888073561</v>
+        <v>0.0002639718154793195</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001517993437197559</v>
+        <v>0.0001522440219719928</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001382807890809243</v>
+        <v>0.000208108898041712</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004858964087887135</v>
+        <v>0.003491735901940851</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02103564891510849</v>
+        <v>0.008352449118784203</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000526161002739</v>
+        <v>1.000082953460196</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02193118003922094</v>
+        <v>0.008708030169724093</v>
       </c>
       <c r="P10" t="n">
-        <v>131.4461468524462</v>
+        <v>135.1408019019473</v>
       </c>
       <c r="Q10" t="n">
-        <v>202.1409446948018</v>
+        <v>205.8355997443029</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_9</t>
+          <t>model_25_5_15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9992546064558395</v>
+        <v>0.9998841591382903</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7129380490550647</v>
+        <v>0.7053533034626018</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9968374856310183</v>
+        <v>0.9989662270649088</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9961536350289732</v>
+        <v>0.999138379564113</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9967769635278959</v>
+        <v>0.9996250442058084</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0004424978071381455</v>
+        <v>6.876813957555919e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1704123745115142</v>
+        <v>0.1749150071391496</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001247608479393214</v>
+        <v>0.0002564613086824747</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001518002813837018</v>
+        <v>0.0001488641113329306</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001382809248778097</v>
+        <v>0.0002026627100077026</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004858963824944504</v>
+        <v>0.003504592201881329</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02103563184546986</v>
+        <v>0.008292655761308266</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000526160148819</v>
+        <v>1.00008177002003</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02193116224289245</v>
+        <v>0.008645691285231093</v>
       </c>
       <c r="P11" t="n">
-        <v>131.4461500982972</v>
+        <v>135.1695400156954</v>
       </c>
       <c r="Q11" t="n">
-        <v>202.1409479406528</v>
+        <v>205.864337858051</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_12</t>
+          <t>model_25_5_14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9992545993176417</v>
+        <v>0.9998858307766236</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7129380303097411</v>
+        <v>0.7052633375054183</v>
       </c>
       <c r="D12" t="n">
-        <v>0.996837444206394</v>
+        <v>0.9989994814993453</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9961536079503374</v>
+        <v>0.9991599015723446</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9967769326621793</v>
+        <v>0.999636115725684</v>
       </c>
       <c r="G12" t="n">
-        <v>0.00044250204468078</v>
+        <v>6.77757828498506e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1704123856395481</v>
+        <v>0.1749684148176608</v>
       </c>
       <c r="I12" t="n">
-        <v>0.001247624821362417</v>
+        <v>0.0002482114546907781</v>
       </c>
       <c r="J12" t="n">
-        <v>0.001518013500666207</v>
+        <v>0.0001451457052969803</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001382822491382951</v>
+        <v>0.0001966785799938792</v>
       </c>
       <c r="L12" t="n">
-        <v>0.004858977222535732</v>
+        <v>0.00351862271305253</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02103573256819881</v>
+        <v>0.00823260486418792</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000526165187547</v>
+        <v>1.00008059004003</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02193126725359649</v>
+        <v>0.008583083897097839</v>
       </c>
       <c r="P12" t="n">
-        <v>131.4461309455589</v>
+        <v>135.1986112238583</v>
       </c>
       <c r="Q12" t="n">
-        <v>202.1409287879145</v>
+        <v>205.893409066214</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_23</t>
+          <t>model_25_5_13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9992546008794934</v>
+        <v>0.9998874495148173</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7129380297398531</v>
+        <v>0.7051608435152907</v>
       </c>
       <c r="D13" t="n">
-        <v>0.996837444206394</v>
+        <v>0.9990359491069172</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9961536226334967</v>
+        <v>0.9991835839054301</v>
       </c>
       <c r="F13" t="n">
-        <v>0.996776939415456</v>
+        <v>0.9996482701656778</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0004425011174981251</v>
+        <v>6.681482993222559e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1704123859778582</v>
+        <v>0.1750292596777103</v>
       </c>
       <c r="I13" t="n">
-        <v>0.001247624821362417</v>
+        <v>0.0002391644676349697</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001518007705824259</v>
+        <v>0.0001410540550502858</v>
       </c>
       <c r="K13" t="n">
-        <v>0.001382819593961976</v>
+        <v>0.0001901091342460617</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004858959423168995</v>
+        <v>0.003534104252199825</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02103571052990902</v>
+        <v>0.008174033883721402</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000526164085064</v>
+        <v>1.000079447401305</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02193124427709108</v>
+        <v>0.008522019428734217</v>
       </c>
       <c r="P13" t="n">
-        <v>131.4461351362</v>
+        <v>135.2271709941754</v>
       </c>
       <c r="Q13" t="n">
-        <v>202.1409329785556</v>
+        <v>205.921968836531</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_13</t>
+          <t>model_25_5_12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9992546008794934</v>
+        <v>0.9998889512169444</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7129380297398531</v>
+        <v>0.705043783003197</v>
       </c>
       <c r="D14" t="n">
-        <v>0.996837444206394</v>
+        <v>0.9990758614123045</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9961536226334967</v>
+        <v>0.9992095883679156</v>
       </c>
       <c r="F14" t="n">
-        <v>0.996776939415456</v>
+        <v>0.9996615858148082</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0004425011174981251</v>
+        <v>6.592335467943219e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1704123859778582</v>
+        <v>0.1750987518544399</v>
       </c>
       <c r="I14" t="n">
-        <v>0.001247624821362417</v>
+        <v>0.0002292629102187185</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001518007705824259</v>
+        <v>0.0001365612052554366</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001382819593961976</v>
+        <v>0.0001829120577370775</v>
       </c>
       <c r="L14" t="n">
-        <v>0.004858959423168995</v>
+        <v>0.003551052394194358</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02103571052990902</v>
+        <v>0.008119319840936936</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000526164085064</v>
+        <v>1.000078387376274</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02193124427709108</v>
+        <v>0.008464976095874733</v>
       </c>
       <c r="P14" t="n">
-        <v>131.4461351362</v>
+        <v>135.2540355669933</v>
       </c>
       <c r="Q14" t="n">
-        <v>202.1409329785556</v>
+        <v>205.9488334093489</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_14</t>
+          <t>model_25_5_11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9992546008794934</v>
+        <v>0.9998902537049021</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7129380297398531</v>
+        <v>0.7049096407378563</v>
       </c>
       <c r="D15" t="n">
-        <v>0.996837444206394</v>
+        <v>0.999119509074758</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9961536226334967</v>
+        <v>0.9992380832487632</v>
       </c>
       <c r="F15" t="n">
-        <v>0.996776939415456</v>
+        <v>0.9996761569804412</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0004425011174981251</v>
+        <v>6.515014156316229e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1704123859778582</v>
+        <v>0.1751783844977903</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001247624821362417</v>
+        <v>0.000218434674874414</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001518007705824259</v>
+        <v>0.0001316380802479099</v>
       </c>
       <c r="K15" t="n">
-        <v>0.001382819593961976</v>
+        <v>0.000175036377561162</v>
       </c>
       <c r="L15" t="n">
-        <v>0.004858959423168995</v>
+        <v>0.003569445022285182</v>
       </c>
       <c r="M15" t="n">
-        <v>0.02103571052990902</v>
+        <v>0.008071563761946151</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000526164085064</v>
+        <v>1.00007746797301</v>
       </c>
       <c r="O15" t="n">
-        <v>0.02193124427709108</v>
+        <v>0.008415186941732598</v>
       </c>
       <c r="P15" t="n">
-        <v>131.4461351362</v>
+        <v>135.2776321630306</v>
       </c>
       <c r="Q15" t="n">
-        <v>202.1409329785556</v>
+        <v>205.9724300053863</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_15</t>
+          <t>model_25_5_10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9992546008794934</v>
+        <v>0.999891246638286</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7129380297398531</v>
+        <v>0.70475541264688</v>
       </c>
       <c r="D16" t="n">
-        <v>0.996837444206394</v>
+        <v>0.9991670493165115</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9961536226334967</v>
+        <v>0.9992693173331771</v>
       </c>
       <c r="F16" t="n">
-        <v>0.996776939415456</v>
+        <v>0.9996920578627158</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0004425011174981251</v>
+        <v>6.456069341402323e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1704123859778582</v>
+        <v>0.1752699409549005</v>
       </c>
       <c r="I16" t="n">
-        <v>0.001247624821362417</v>
+        <v>0.000206640757466319</v>
       </c>
       <c r="J16" t="n">
-        <v>0.001518007705824259</v>
+        <v>0.0001262416968452877</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001382819593961976</v>
+        <v>0.0001664419887206983</v>
       </c>
       <c r="L16" t="n">
-        <v>0.004858959423168995</v>
+        <v>0.003589567331846082</v>
       </c>
       <c r="M16" t="n">
-        <v>0.02103571052990902</v>
+        <v>0.008034966920530739</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000526164085064</v>
+        <v>1.000076767078857</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02193124427709108</v>
+        <v>0.008377032097012228</v>
       </c>
       <c r="P16" t="n">
-        <v>131.4461351362</v>
+        <v>135.295809586893</v>
       </c>
       <c r="Q16" t="n">
-        <v>202.1409329785556</v>
+        <v>205.9906074292487</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_16</t>
+          <t>model_25_5_9</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9992546008794934</v>
+        <v>0.9998917805294494</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7129380297398531</v>
+        <v>0.7045775374787397</v>
       </c>
       <c r="D17" t="n">
-        <v>0.996837444206394</v>
+        <v>0.999218701748758</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9961536226334967</v>
+        <v>0.9993034168554297</v>
       </c>
       <c r="F17" t="n">
-        <v>0.996776939415456</v>
+        <v>0.9997093621202746</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004425011174981251</v>
+        <v>6.424375255656476e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1704123859778582</v>
+        <v>0.1753755353385157</v>
       </c>
       <c r="I17" t="n">
-        <v>0.001247624821362417</v>
+        <v>0.0001938266762296</v>
       </c>
       <c r="J17" t="n">
-        <v>0.001518007705824259</v>
+        <v>0.0001203502452668785</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001382819593961976</v>
+        <v>0.0001570890788954015</v>
       </c>
       <c r="L17" t="n">
-        <v>0.004858959423168995</v>
+        <v>0.003611323778933875</v>
       </c>
       <c r="M17" t="n">
-        <v>0.02103571052990902</v>
+        <v>0.008015220056652516</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000526164085064</v>
+        <v>1.000076390214506</v>
       </c>
       <c r="O17" t="n">
-        <v>0.02193124427709108</v>
+        <v>0.008356444568257064</v>
       </c>
       <c r="P17" t="n">
-        <v>131.4461351362</v>
+        <v>135.3056521507808</v>
       </c>
       <c r="Q17" t="n">
-        <v>202.1409329785556</v>
+        <v>206.0004499931365</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_17</t>
+          <t>model_25_5_8</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9992546008794934</v>
+        <v>0.999891664100051</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7129380297398531</v>
+        <v>0.7043714045774867</v>
       </c>
       <c r="D18" t="n">
-        <v>0.996837444206394</v>
+        <v>0.9992745289595437</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9961536226334967</v>
+        <v>0.9993405435635622</v>
       </c>
       <c r="F18" t="n">
-        <v>0.996776939415456</v>
+        <v>0.9997281091724298</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0004425011174981251</v>
+        <v>6.431287007690204e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1704123859778582</v>
+        <v>0.1754979047331772</v>
       </c>
       <c r="I18" t="n">
-        <v>0.001247624821362417</v>
+        <v>0.0001799769041450521</v>
       </c>
       <c r="J18" t="n">
-        <v>0.001518007705824259</v>
+        <v>0.0001139357799377501</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001382819593961976</v>
+        <v>0.0001469563420414011</v>
       </c>
       <c r="L18" t="n">
-        <v>0.004858959423168995</v>
+        <v>0.003634841965750864</v>
       </c>
       <c r="M18" t="n">
-        <v>0.02103571052990902</v>
+        <v>0.00801953053968261</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000526164085064</v>
+        <v>1.000076472399964</v>
       </c>
       <c r="O18" t="n">
-        <v>0.02193124427709108</v>
+        <v>0.008360938557473678</v>
       </c>
       <c r="P18" t="n">
-        <v>131.4461351362</v>
+        <v>135.3035015800648</v>
       </c>
       <c r="Q18" t="n">
-        <v>202.1409329785556</v>
+        <v>205.9982994224204</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_18</t>
+          <t>model_25_5_7</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9992546008794934</v>
+        <v>0.9998906439248202</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7129380297398531</v>
+        <v>0.704131616219338</v>
       </c>
       <c r="D19" t="n">
-        <v>0.996837444206394</v>
+        <v>0.9993346138661588</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9961536226334967</v>
+        <v>0.9993808898042834</v>
       </c>
       <c r="F19" t="n">
-        <v>0.996776939415456</v>
+        <v>0.9997483457117261</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004425011174981251</v>
+        <v>6.491849016321693e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1704123859778582</v>
+        <v>0.175640253460892</v>
       </c>
       <c r="I19" t="n">
-        <v>0.001247624821362417</v>
+        <v>0.000165070870857183</v>
       </c>
       <c r="J19" t="n">
-        <v>0.001518007705824259</v>
+        <v>0.0001069650686820364</v>
       </c>
       <c r="K19" t="n">
-        <v>0.001382819593961976</v>
+        <v>0.0001360185409498971</v>
       </c>
       <c r="L19" t="n">
-        <v>0.004858959423168995</v>
+        <v>0.003660308152064921</v>
       </c>
       <c r="M19" t="n">
-        <v>0.02103571052990902</v>
+        <v>0.008057201137070921</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000526164085064</v>
+        <v>1.000077192523656</v>
       </c>
       <c r="O19" t="n">
-        <v>0.02193124427709108</v>
+        <v>0.008400212870181698</v>
       </c>
       <c r="P19" t="n">
-        <v>131.4461351362</v>
+        <v>135.2847561449408</v>
       </c>
       <c r="Q19" t="n">
-        <v>202.1409329785556</v>
+        <v>205.9795539872964</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_19</t>
+          <t>model_25_5_6</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9992546008794934</v>
+        <v>0.9998884061773464</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7129380297398531</v>
+        <v>0.7038510613749041</v>
       </c>
       <c r="D20" t="n">
-        <v>0.996837444206394</v>
+        <v>0.9993988767020947</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9961536226334967</v>
+        <v>0.9994245545295297</v>
       </c>
       <c r="F20" t="n">
-        <v>0.996776939415456</v>
+        <v>0.9997700735613217</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0004425011174981251</v>
+        <v>6.624691372930374e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1704123859778582</v>
+        <v>0.1758068029358863</v>
       </c>
       <c r="I20" t="n">
-        <v>0.001247624821362417</v>
+        <v>0.0001491283650666701</v>
       </c>
       <c r="J20" t="n">
-        <v>0.001518007705824259</v>
+        <v>9.942101534990948e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.001382819593961976</v>
+        <v>0.0001242746902082898</v>
       </c>
       <c r="L20" t="n">
-        <v>0.004858959423168995</v>
+        <v>0.003687617893489895</v>
       </c>
       <c r="M20" t="n">
-        <v>0.02103571052990902</v>
+        <v>0.008139220707740006</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000526164085064</v>
+        <v>1.000078772110108</v>
       </c>
       <c r="O20" t="n">
-        <v>0.02193124427709108</v>
+        <v>0.008485724183778085</v>
       </c>
       <c r="P20" t="n">
-        <v>131.4461351362</v>
+        <v>135.2442433588022</v>
       </c>
       <c r="Q20" t="n">
-        <v>202.1409329785556</v>
+        <v>205.9390412011579</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_20</t>
+          <t>model_25_5_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9992546008794934</v>
+        <v>0.9998845188967035</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7129380297398531</v>
+        <v>0.7035212733159749</v>
       </c>
       <c r="D21" t="n">
-        <v>0.996837444206394</v>
+        <v>0.9994670328637997</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9961536226334967</v>
+        <v>0.9994715028769783</v>
       </c>
       <c r="F21" t="n">
-        <v>0.996776939415456</v>
+        <v>0.9997932186639261</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0004425011174981251</v>
+        <v>6.855457144070826e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1704123859778582</v>
+        <v>0.176002579373769</v>
       </c>
       <c r="I21" t="n">
-        <v>0.001247624821362417</v>
+        <v>0.0001322199920262363</v>
       </c>
       <c r="J21" t="n">
-        <v>0.001518007705824259</v>
+        <v>9.13096431837175e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.001382819593961976</v>
+        <v>0.0001117648176049769</v>
       </c>
       <c r="L21" t="n">
-        <v>0.004858959423168995</v>
+        <v>0.003716874343633476</v>
       </c>
       <c r="M21" t="n">
-        <v>0.02103571052990902</v>
+        <v>0.008279768803578291</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000526164085064</v>
+        <v>1.000081516072915</v>
       </c>
       <c r="O21" t="n">
-        <v>0.02193124427709108</v>
+        <v>0.00863225570303087</v>
       </c>
       <c r="P21" t="n">
-        <v>131.4461351362</v>
+        <v>135.1757609329918</v>
       </c>
       <c r="Q21" t="n">
-        <v>202.1409329785556</v>
+        <v>205.8705587753475</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_21</t>
+          <t>model_25_5_4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9992546008794934</v>
+        <v>0.9998784437201894</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7129380297398531</v>
+        <v>0.7031309151796694</v>
       </c>
       <c r="D22" t="n">
-        <v>0.996837444206394</v>
+        <v>0.9995384876974008</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9961536226334967</v>
+        <v>0.9995218246132279</v>
       </c>
       <c r="F22" t="n">
-        <v>0.996776939415456</v>
+        <v>0.9998176601700065</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0004425011174981251</v>
+        <v>7.216105865343984e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1704123859778582</v>
+        <v>0.1762343128260733</v>
       </c>
       <c r="I22" t="n">
-        <v>0.001247624821362417</v>
+        <v>0.0001144932751477097</v>
       </c>
       <c r="J22" t="n">
-        <v>0.001518007705824259</v>
+        <v>8.261544300515736e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.001382819593961976</v>
+        <v>9.855424202338911e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.004858959423168995</v>
+        <v>0.003748133615330214</v>
       </c>
       <c r="M22" t="n">
-        <v>0.02103571052990902</v>
+        <v>0.008494766544964014</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000526164085064</v>
+        <v>1.000085804432807</v>
       </c>
       <c r="O22" t="n">
-        <v>0.02193124427709108</v>
+        <v>0.008856406343374063</v>
       </c>
       <c r="P22" t="n">
-        <v>131.4461351362</v>
+        <v>135.0732200227991</v>
       </c>
       <c r="Q22" t="n">
-        <v>202.1409329785556</v>
+        <v>205.7680178651547</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_22</t>
+          <t>model_25_5_3</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9992546008794934</v>
+        <v>0.9998694789190288</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7129380297398531</v>
+        <v>0.7026660515190809</v>
       </c>
       <c r="D23" t="n">
-        <v>0.996837444206394</v>
+        <v>0.9996123760288889</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9961536226334967</v>
+        <v>0.9995752453880749</v>
       </c>
       <c r="F23" t="n">
-        <v>0.996776939415456</v>
+        <v>0.9998431550283167</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0004425011174981251</v>
+        <v>7.748295188165148e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1704123859778582</v>
+        <v>0.1765102759760633</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001247624821362417</v>
+        <v>9.616284924223284e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.001518007705824259</v>
+        <v>7.338581491943214e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.001382819593961976</v>
+        <v>8.477433208083248e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.004858959423168995</v>
+        <v>0.003781511932151623</v>
       </c>
       <c r="M23" t="n">
-        <v>0.02103571052990902</v>
+        <v>0.008802440109518013</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000526164085064</v>
+        <v>1.000092132527744</v>
       </c>
       <c r="O23" t="n">
-        <v>0.02193124427709108</v>
+        <v>0.009177178208543206</v>
       </c>
       <c r="P23" t="n">
-        <v>131.4461351362</v>
+        <v>134.9309052430476</v>
       </c>
       <c r="Q23" t="n">
-        <v>202.1409329785556</v>
+        <v>205.6257030854032</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_24</t>
+          <t>model_25_5_2</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9992546008794934</v>
+        <v>0.9998567175112791</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7129380297398531</v>
+        <v>0.7021088677787647</v>
       </c>
       <c r="D24" t="n">
-        <v>0.996837444206394</v>
+        <v>0.9996873178404376</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9961536226334967</v>
+        <v>0.9996314457045808</v>
       </c>
       <c r="F24" t="n">
-        <v>0.996776939415456</v>
+        <v>0.9998693368455946</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0004425011174981251</v>
+        <v>8.505867478594938e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1704123859778582</v>
+        <v>0.1768410443133993</v>
       </c>
       <c r="I24" t="n">
-        <v>0.001247624821362417</v>
+        <v>7.757107302868049e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.001518007705824259</v>
+        <v>6.36759591350892e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.001382819593961976</v>
+        <v>7.062312245912166e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.004858959423168995</v>
+        <v>0.003817135219643262</v>
       </c>
       <c r="M24" t="n">
-        <v>0.02103571052990902</v>
+        <v>0.009222725995384953</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000526164085064</v>
+        <v>1.000101140580274</v>
       </c>
       <c r="O24" t="n">
-        <v>0.02193124427709108</v>
+        <v>0.009615356534683225</v>
       </c>
       <c r="P24" t="n">
-        <v>131.4461351362</v>
+        <v>134.7443384960324</v>
       </c>
       <c r="Q24" t="n">
-        <v>202.1409329785556</v>
+        <v>205.439136338388</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_7</t>
+          <t>model_25_5_1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.999254607682264</v>
+        <v>0.9998389824178405</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7129380283982553</v>
+        <v>0.7014363916691021</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9968374893545581</v>
+        <v>0.9997612037947713</v>
       </c>
       <c r="E25" t="n">
-        <v>0.996153641460413</v>
+        <v>0.9996896704110687</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9967769772272674</v>
+        <v>0.9998955990822552</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0004424970790796162</v>
+        <v>9.558699236723865e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1704123867742887</v>
+        <v>0.1772402551815503</v>
       </c>
       <c r="I25" t="n">
-        <v>0.001247607010460814</v>
+        <v>5.924123685436443e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.00151800027561101</v>
+        <v>5.361634491528253e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.001382803371209595</v>
+        <v>5.642844635345791e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.004858990571654846</v>
+        <v>0.003855659070073578</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0210356145400988</v>
+        <v>0.009776860046417696</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000526159283108</v>
+        <v>1.00011365946976</v>
       </c>
       <c r="O25" t="n">
-        <v>0.02193114420079592</v>
+        <v>0.01019308121948405</v>
       </c>
       <c r="P25" t="n">
-        <v>131.4461533889762</v>
+        <v>134.5109476205371</v>
       </c>
       <c r="Q25" t="n">
-        <v>202.1409512313318</v>
+        <v>205.2057454628927</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_25_5_11</t>
+          <t>model_25_5_0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.999254603181486</v>
+        <v>0.9998147630406968</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7129380101081015</v>
+        <v>0.7006204941740813</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9968374447229409</v>
+        <v>0.9998312015466178</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9961536423815557</v>
+        <v>0.9997488640102447</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9967769577652812</v>
+        <v>0.9999211235736389</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0004424997509359061</v>
+        <v>0.0001099646608623448</v>
       </c>
       <c r="H26" t="n">
-        <v>0.170412397632114</v>
+        <v>0.1777246071795313</v>
       </c>
       <c r="I26" t="n">
-        <v>0.001247624617585242</v>
+        <v>4.187599693174435e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.001517999912073701</v>
+        <v>4.338933291450135e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.001382811721166178</v>
+        <v>4.263251980550164e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.004858986964370364</v>
+        <v>0.003898279843467463</v>
       </c>
       <c r="M26" t="n">
-        <v>0.02103567804792387</v>
+        <v>0.01048640361908433</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000526162460128</v>
+        <v>1.000130755500685</v>
       </c>
       <c r="O26" t="n">
-        <v>0.02193121041228058</v>
+        <v>0.01093283153099678</v>
       </c>
       <c r="P26" t="n">
-        <v>131.4461413127463</v>
+        <v>134.2307030173525</v>
       </c>
       <c r="Q26" t="n">
-        <v>202.1409391551019</v>
+        <v>204.9255008597081</v>
       </c>
     </row>
   </sheetData>
